--- a/57.xlsx
+++ b/57.xlsx
@@ -511,7 +511,7 @@
         <v>0.304724782705307</v>
       </c>
       <c r="K2" t="n">
-        <v>1.120819999778178e-05</v>
+        <v>8.92160000057629e-06</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>0.3108069598674774</v>
       </c>
       <c r="K3" t="n">
-        <v>5.895899997995002e-06</v>
+        <v>5.276599999888276e-06</v>
       </c>
     </row>
     <row r="4">
@@ -593,7 +593,7 @@
         <v>0.3064090311527252</v>
       </c>
       <c r="K4" t="n">
-        <v>5.980300000373973e-06</v>
+        <v>5.441999999675318e-06</v>
       </c>
     </row>
     <row r="5">
@@ -634,7 +634,7 @@
         <v>0.3084602057933807</v>
       </c>
       <c r="K5" t="n">
-        <v>5.796500001451932e-06</v>
+        <v>5.736699999943085e-06</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>0.3026606142520905</v>
       </c>
       <c r="K6" t="n">
-        <v>5.2213999988453e-06</v>
+        <v>5.561500000112573e-06</v>
       </c>
     </row>
     <row r="7">
@@ -716,7 +716,7 @@
         <v>0.2876628041267395</v>
       </c>
       <c r="K7" t="n">
-        <v>6.747499999619322e-06</v>
+        <v>5.636199999571545e-06</v>
       </c>
     </row>
     <row r="8">
@@ -757,7 +757,7 @@
         <v>0.281400203704834</v>
       </c>
       <c r="K8" t="n">
-        <v>6.228799997188617e-06</v>
+        <v>5.251100000350561e-06</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.2835347056388855</v>
       </c>
       <c r="K9" t="n">
-        <v>7.011900001089088e-06</v>
+        <v>8.142099999531638e-06</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.2849827110767365</v>
       </c>
       <c r="K10" t="n">
-        <v>5.695800002285978e-06</v>
+        <v>6.511800000225776e-06</v>
       </c>
     </row>
     <row r="11">
@@ -880,7 +880,7 @@
         <v>0.2848705351352692</v>
       </c>
       <c r="K11" t="n">
-        <v>5.271400001220172e-06</v>
+        <v>5.69550000000163e-06</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         <v>0.3029690682888031</v>
       </c>
       <c r="K12" t="n">
-        <v>5.687699998816242e-06</v>
+        <v>5.606300000181363e-06</v>
       </c>
     </row>
     <row r="13">
@@ -962,7 +962,7 @@
         <v>0.3073286116123199</v>
       </c>
       <c r="K13" t="n">
-        <v>5.66140000228188e-06</v>
+        <v>5.14019999991433e-06</v>
       </c>
     </row>
     <row r="14">
@@ -1003,7 +1003,7 @@
         <v>0.305938184261322</v>
       </c>
       <c r="K14" t="n">
-        <v>5.294800001138355e-06</v>
+        <v>5.721300000004703e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1044,7 +1044,7 @@
         <v>0.3058680295944214</v>
       </c>
       <c r="K15" t="n">
-        <v>5.579500000749249e-06</v>
+        <v>5.885399999897345e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1085,7 +1085,7 @@
         <v>0.3027482926845551</v>
       </c>
       <c r="K16" t="n">
-        <v>5.817500001285225e-06</v>
+        <v>5.530399999770452e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1126,7 +1126,7 @@
         <v>0.3149725496768951</v>
       </c>
       <c r="K17" t="n">
-        <v>9.663999997428619e-06</v>
+        <v>9.866100000181177e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1167,7 +1167,7 @@
         <v>0.3141289055347443</v>
       </c>
       <c r="K18" t="n">
-        <v>8.207999999285675e-06</v>
+        <v>7.995199999641045e-06</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>0.3117594718933105</v>
       </c>
       <c r="K19" t="n">
-        <v>7.890400000178488e-06</v>
+        <v>8.241499999712687e-06</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.3145458400249481</v>
       </c>
       <c r="K20" t="n">
-        <v>7.74019999880693e-06</v>
+        <v>7.749999999759894e-06</v>
       </c>
     </row>
     <row r="21">
@@ -1290,7 +1290,7 @@
         <v>0.3127709329128265</v>
       </c>
       <c r="K21" t="n">
-        <v>7.438700002239784e-06</v>
+        <v>7.365100000242819e-06</v>
       </c>
     </row>
     <row r="22">
@@ -1331,7 +1331,7 @@
         <v>0.2798687517642975</v>
       </c>
       <c r="K22" t="n">
-        <v>9.114800002862466e-06</v>
+        <v>7.325500000661122e-06</v>
       </c>
     </row>
     <row r="23">
@@ -1372,7 +1372,7 @@
         <v>0.294763058423996</v>
       </c>
       <c r="K23" t="n">
-        <v>8.26260000030743e-06</v>
+        <v>7.834699999875738e-06</v>
       </c>
     </row>
     <row r="24">
@@ -1413,7 +1413,7 @@
         <v>0.302911102771759</v>
       </c>
       <c r="K24" t="n">
-        <v>7.262600000103703e-06</v>
+        <v>7.740000000012514e-06</v>
       </c>
     </row>
     <row r="25">
@@ -1454,7 +1454,7 @@
         <v>0.2694041430950165</v>
       </c>
       <c r="K25" t="n">
-        <v>7.91409999874304e-06</v>
+        <v>8.065099999839731e-06</v>
       </c>
     </row>
     <row r="26">
@@ -1495,7 +1495,7 @@
         <v>0.2688374519348145</v>
       </c>
       <c r="K26" t="n">
-        <v>8.18269999945187e-06</v>
+        <v>7.847799999581184e-06</v>
       </c>
     </row>
   </sheetData>
